--- a/TestCases/Medical_History_TestCase.xlsx
+++ b/TestCases/Medical_History_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A220442-7DE1-47E9-990C-C9FBB846A8B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529646F6-43BC-4B19-A378-2793D62F90C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HISTORY" sheetId="10" r:id="rId1"/>
+    <sheet name="HISTORY" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -34,19 +34,19 @@
     <t>SpringMediCareWeb</t>
   </si>
   <si>
-    <t>Module Code：</t>
+    <t>Pass</t>
   </si>
   <si>
-    <t>Test requirement:</t>
-  </si>
-  <si>
-    <t>Pass</t>
+    <t>Fail</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>Module Code：</t>
+  </si>
+  <si>
+    <t>Test requirement:</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -85,10 +85,10 @@
     <t>Retest Evidence</t>
   </si>
   <si>
-    <t>MEDICAL400 - Medical Record Management</t>
+    <t>MEDICAL - Medical History</t>
   </si>
   <si>
-    <t>MEDICAL1 - Examination and Medical Record Management</t>
+    <t>Patient Medical History</t>
   </si>
   <si>
     <t>1. Kiểm tra thời điểm phát sinh lịch sử khám bệnh</t>
@@ -97,15 +97,16 @@
     <t>TC-MEDICALHISTORY-001</t>
   </si>
   <si>
-    <t>Kiểm tra lịch hẹn mới được Patient tạo nhưng chưa được Doctor khám không được ghi nhận vào Lịch sử khám bệnh.</t>
+    <t>Kiểm tra lịch hẹn chưa được Doctor khám không phát sinh Lịch sử khám bệnh.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
-2: Mở trang Lịch sử khám bệnh.
-3: Kiểm tra danh sách lịch sử khám.</t>
+    <t>1: Đăng nhập bằng tài khoản Patient.
+2: Tạo một lịch hẹn hợp lệ.
+3: Mở trang Lịch sử khám bệnh.
+4: Kiểm tra lịch hẹn vừa tạo trong danh sách lịch sử khám.</t>
   </si>
   <si>
-    <t>Lịch hẹn mới chưa xuất hiện trong Lịch sử khám bệnh.
+    <t>Lịch hẹn vừa tạo chưa xuất hiện trong Lịch sử khám bệnh.
 Không phát sinh bản ghi khám bệnh khi Doctor chưa thực hiện khám.</t>
   </si>
   <si>
@@ -118,15 +119,16 @@
     <t>TC-MEDICALHISTORY-002</t>
   </si>
   <si>
-    <t>Kiểm tra việc Admin xác nhận lịch hẹn không tự động tạo lịch sử khám bệnh khi Doctor chưa thực hiện khám.</t>
+    <t>Kiểm tra lịch hẹn đã được Admin xác nhận nhưng chưa được Doctor khám không phát sinh Lịch sử khám bệnh.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
-2: Đăng nhập bằng Admin và xác nhận lịch hẹn vừa tạo.
-3: Đăng nhập lại bằng Patient.
-4: Mở trang Lịch hẹn của tôi và xác nhận lịch đang ở trạng thái Đã xác nhận.
-5: Mở trang Lịch sử khám bệnh.
-6: Kiểm tra danh sách lịch sử khám.</t>
+    <t>1: Đăng nhập bằng tài khoản Patient.
+2: Tạo một lịch hẹn hợp lệ.
+3: Đăng xuất và đăng nhập bằng tài khoản Admin.
+4: Xác nhận lịch hẹn vừa tạo.
+5: Đăng xuất và đăng nhập lại bằng tài khoản Patient.
+6: Mở trang Lịch sử khám bệnh.
+7: Kiểm tra lịch hẹn vừa được xác nhận trong danh sách lịch sử khám</t>
   </si>
   <si>
     <t>Lịch hẹn đã xác nhận chưa xuất hiện trong Lịch sử khám bệnh.
@@ -145,22 +147,24 @@
     <t>TC-MEDICALHISTORY-003</t>
   </si>
   <si>
-    <t>Kiểm tra hệ thống ghi nhận lần khám mới vào Lịch sử khám bệnh sau khi Doctor hoàn thành khám và lưu hồ sơ bệnh án.</t>
+    <t>Kiểm tra Lịch sử khám bệnh được tạo sau khi Doctor hoàn thành khám và lưu hồ sơ bệnh án.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
-2: Admin xác nhận lịch hẹn vừa tạo.
-3: Đăng nhập bằng Doctor được Patient đặt lịch.
-4: Mở lịch hẹn và chọn Khám bệnh.
-5: Nhập chẩn đoán, hướng điều trị hợp lệ và lưu hồ sơ bệnh án.
-6: Đăng nhập lại bằng Patient.
-7: Mở trang Lịch sử khám bệnh.
-8: Tìm lần khám vừa được Doctor hoàn thành.</t>
+    <t>1: Đăng nhập bằng tài khoản Patient.
+2: Tạo một lịch hẹn hợp lệ.
+3: Đăng xuất và đăng nhập bằng tài khoản Admin.
+4: Xác nhận lịch hẹn vừa tạo.
+5: Đăng xuất và đăng nhập bằng tài khoản Doctor phụ trách lịch hẹn.
+6: Mở lịch hẹn và chọn Khám bệnh.
+7: Nhập thông tin khám và lưu hồ sơ bệnh án.
+8: Đăng xuất và đăng nhập lại bằng tài khoản Patient.
+9: Mở trang Lịch sử khám bệnh.
+10: Kiểm tra bản ghi của lần khám vừa hoàn thành.</t>
   </si>
   <si>
-    <t>Lần khám mới xuất hiện trong Lịch sử khám bệnh của Patient.
+    <t>Lần khám vừa hoàn thành xuất hiện trong Lịch sử khám bệnh của Patient.
 Bản ghi thuộc đúng Patient và Doctor thực hiện khám.
-Không tạo bản ghi trước thời điểm Doctor lưu kết quả khám.</t>
+Thông tin lần khám được ghi nhận sau khi Doctor lưu hồ sơ bệnh án.</t>
   </si>
   <si>
     <t>TCMedicalHistory3_1, TCMedicalHistory3_2, TCMedicalHistory3_3</t>
@@ -175,20 +179,19 @@
     <t>TC-MEDICALHISTORY-004</t>
   </si>
   <si>
-    <t>Kiểm tra một bản ghi của lịch sử khám bệnh</t>
+    <t>Kiểm tra thông tin chi tiết của một bản ghi Lịch sử khám bệnh.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị Patient có ít nhất một bản ghi trong Lịch sử khám bệnh.
-2: Đăng nhập Patient.
-3: Mở Lịch sử khám bệnh.
-4: Chọn một bản ghi và ghi nhận ID.
-5: Nhấn Xem chi tiết.
-6: Kiểm tra nội dung trang chi tiết.</t>
+    <t>1: Đăng nhập bằng tài khoản Patient đã có Lịch sử khám bệnh.
+2: Mở trang Lịch sử khám bệnh.
+3: Chọn một bản ghi và ghi nhận thông tin nhận diện của bản ghi.
+4: Nhấn Xem chi tiết.
+5: Kiểm tra trang chi tiết của bản ghi vừa chọn.</t>
   </si>
   <si>
-    <t>Mở đúng hồ sơ của record đã chọn.
-Hiển thị đầy đủ thông tin hồ sơ.
-Thông tin tương ứng đúng với record được chọn.</t>
+    <t>Hệ thống mở đúng hồ sơ của bản ghi đã chọn.
+Trang chi tiết hiển thị đầy đủ thông tin của hồ sơ.
+Thông tin hiển thị tương ứng với bản ghi được chọn.</t>
   </si>
   <si>
     <t>TCMedicalHistory4_1, TCMedicalHistory4-2</t>
@@ -206,7 +209,7 @@
     <t>TC-MEDICALHISTORY-005</t>
   </si>
   <si>
-    <t>Kiểm tra mỗi Patient chỉ nhìn thấy các bản ghi Lịch sử khám bệnh thuộc tài khoản của mình.</t>
+    <t>Kiểm tra Lịch sử khám bệnh được phân tách theo từng Patient.</t>
   </si>
   <si>
     <t>1: Đăng nhập bằng Patient A.
@@ -217,9 +220,9 @@
 6: So sánh danh sách lịch sử khám của hai Patient.</t>
   </si>
   <si>
-    <t>Mỗi Patient hiển thị đúng lịch sử khám bệnh thuộc tài khoản của mình.
-Danh sách của Patient A và Patient B được phân tách riêng.
-Không xuất hiện bản ghi của Patient A trong lịch sử của Patient B và ngược lại.</t>
+    <t>Mỗi Patient chỉ nhìn thấy các bản ghi Lịch sử khám bệnh thuộc tài khoản của mình.
+Không xuất hiện bản ghi của Patient A trong lịch sử của Patient B và ngược lại.
+Dữ liệu giữa hai Patient được phân tách riêng.</t>
   </si>
   <si>
     <t>TCMedicalHistory5_1, TCMedicalHistory5_2</t>
@@ -234,24 +237,23 @@
     <t>TC-MEDICALHISTORY-006</t>
   </si>
   <si>
-    <t>Kiểm tra thông tin Lịch sử khám bệnh của Patient được cập nhật chính xác sau khi Doctor chỉnh sửa hồ sơ bệnh án đã có.</t>
+    <t>Kiểm tra Lịch sử khám bệnh được cập nhật sau khi Doctor chỉnh sửa hồ sơ bệnh án.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị Patient có ít nhất một hồ sơ bệnh án đã hoàn thành.
-2: Ghi nhận ID, chẩn đoán và hướng điều trị hiện tại của hồ sơ.
-3: Đăng nhập bằng Doctor phụ trách hồ sơ.
+    <t>1: Đăng nhập bằng tài khoản Patient đã có hồ sơ bệnh án hoàn thành.
+2: Mở trang Lịch sử khám bệnh và ghi nhận thông tin của một bản ghi.
+3: Đăng xuất và đăng nhập bằng tài khoản Doctor phụ trách hồ sơ.
 4: Mở hồ sơ bệnh án tương ứng và chọn Cập nhật hồ sơ.
-5: Thay đổi chẩn đoán và hướng điều trị, sau đó lưu.
-6: Đăng nhập lại bằng Patient.
+5: Thay đổi thông tin khám và lưu cập nhật.
+6: Đăng xuất và đăng nhập lại bằng tài khoản Patient.
 7: Mở trang Lịch sử khám bệnh.
 8: Kiểm tra bản ghi vừa được Doctor cập nhật.</t>
   </si>
   <si>
-    <t>Hồ sơ bệnh án được Doctor cập nhật thành công.
-Chẩn đoán và hướng điều trị mới hiển thị đúng trong Lịch sử khám bệnh của Patient.
+    <t>Thông tin đã chỉnh sửa được cập nhật trong Lịch sử khám bệnh của Patient.
 Bản ghi vẫn giữ nguyên ID ban đầu.
 Hệ thống không tạo thêm bản ghi mới sau khi cập nhật hồ sơ.
-Các bản ghi lịch sử khám khác không bị thay đổi.</t>
+Các bản ghi Lịch sử khám bệnh khác không bị thay đổi.</t>
   </si>
   <si>
     <t>TCMedicalHistory6_1, TCMedicalHistory6_2, TCMedicalHistory6_3</t>
@@ -280,10 +282,6 @@
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="MS PGothic"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +291,10 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -493,10 +495,10 @@
   </cellStyleXfs>
   <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -512,10 +514,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -531,8 +533,8 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -541,33 +543,33 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -786,7 +788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -809,9 +811,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -838,9 +840,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -869,11 +871,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -900,13 +902,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="25"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -933,13 +935,13 @@
     </row>
     <row r="5" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="25"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -966,13 +968,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1003,7 +1005,7 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
@@ -1068,21 +1070,21 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="32" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="30" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="35" t="s">
@@ -1119,19 +1121,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1150,17 +1152,17 @@
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1180,18 +1182,18 @@
       <c r="A12" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="25"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="28"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1220,8 +1222,8 @@
       <c r="D13" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1229,7 +1231,7 @@
         <v>46246</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>28</v>
@@ -1252,7 +1254,7 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>29</v>
       </c>
@@ -1265,8 +1267,8 @@
       <c r="D14" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1274,7 +1276,7 @@
         <v>46246</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>34</v>
@@ -1301,18 +1303,18 @@
       <c r="A15" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="25"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="28"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1341,8 +1343,8 @@
       <c r="D16" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="17" t="s">
         <v>40</v>
       </c>
@@ -1350,7 +1352,7 @@
         <v>46246</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>41</v>
@@ -1377,18 +1379,18 @@
       <c r="A17" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="25"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="28"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1417,8 +1419,8 @@
       <c r="D18" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
       <c r="G18" s="17" t="s">
         <v>47</v>
       </c>
@@ -1426,7 +1428,7 @@
         <v>46246</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>48</v>
@@ -1435,7 +1437,7 @@
         <v>46247</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M18" s="17" t="s">
         <v>49</v>
@@ -1459,18 +1461,18 @@
       <c r="A19" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="25"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="28"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -1499,8 +1501,8 @@
       <c r="D20" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
       <c r="G20" s="17" t="s">
         <v>55</v>
       </c>
@@ -1508,7 +1510,7 @@
         <v>46247</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>56</v>
@@ -1535,34 +1537,34 @@
       <c r="A21" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="25"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
       <c r="N21" s="39"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="29"/>
-      <c r="X21" s="29"/>
-      <c r="Y21" s="29"/>
-      <c r="Z21" s="29"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="23"/>
+      <c r="X21" s="23"/>
+      <c r="Y21" s="23"/>
+      <c r="Z21" s="23"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>58</v>
       </c>
@@ -1575,8 +1577,8 @@
       <c r="D22" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="22" t="s">
         <v>62</v>
       </c>
@@ -1584,7 +1586,7 @@
         <v>46247</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>63</v>
@@ -29566,13 +29568,13 @@
     <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
-    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
-    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
-    <hyperlink ref="G18" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
-    <hyperlink ref="M18" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
-    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0900-000005000000}"/>
-    <hyperlink ref="G22" r:id="rId7" xr:uid="{00000000-0004-0000-0900-000006000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
+    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
+    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000002000000}"/>
+    <hyperlink ref="G18" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000003000000}"/>
+    <hyperlink ref="M18" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000004000000}"/>
+    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000005000000}"/>
+    <hyperlink ref="G22" r:id="rId7" xr:uid="{00000000-0004-0000-0A00-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
